--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N17_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.359804944961651</v>
+        <v>1.358468303556268</v>
       </c>
       <c r="D2" t="n">
-        <v>9.554817306469133</v>
+        <v>1.552657812301234</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
